--- a/04_Figures/F04_association/modules/T3/spearman/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T3/spearman/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0107142857142857</v>
+        <v>-0.217857142857143</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0386331240489483</v>
+        <v>-0.804826493639811</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969769876154569</v>
+        <v>0.435392673515538</v>
       </c>
       <c r="G2" t="n">
-        <v>0.989921406880978</v>
+        <v>0.756051387063227</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.464285714285714</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.89006817961079</v>
+        <v>-0.258198889747161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.081250980755495</v>
+        <v>0.800295987397054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.352087583273811</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.532142857142857</v>
+        <v>-0.403571428571428</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.26617607731981</v>
+        <v>-1.59036060370339</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0411585803869344</v>
+        <v>0.135767996503656</v>
       </c>
       <c r="G4" t="n">
-        <v>0.289145387700692</v>
+        <v>0.373361990385055</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0571428571428571</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.206368705447417</v>
+        <v>1.79882257167426</v>
       </c>
       <c r="F5" t="n">
-        <v>0.839699868741576</v>
+        <v>0.0952932131535262</v>
       </c>
       <c r="G5" t="n">
-        <v>0.989921406880978</v>
+        <v>0.349408448229596</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.146428571428571</v>
+        <v>-0.139285714285714</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.533708434419441</v>
+        <v>-0.507145317953373</v>
       </c>
       <c r="F6" t="n">
-        <v>0.602549920983054</v>
+        <v>0.620546087627901</v>
       </c>
       <c r="G6" t="n">
-        <v>0.870349885864411</v>
+        <v>0.75844521821188</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0642857142857143</v>
+        <v>-0.0428571428571429</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.232265873153491</v>
+        <v>-0.154665731331055</v>
       </c>
       <c r="F7" t="n">
-        <v>0.819947965319638</v>
+        <v>0.8794603130259</v>
       </c>
       <c r="G7" t="n">
-        <v>0.989921406880978</v>
+        <v>0.8794603130259</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.307142857142857</v>
+        <v>0.560714285714286</v>
       </c>
       <c r="E8" t="n">
-        <v>1.16366700331215</v>
+        <v>2.44161989115426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.265472685710278</v>
+        <v>0.0296764960944747</v>
       </c>
       <c r="G8" t="n">
-        <v>0.575190819038936</v>
+        <v>0.217618347262522</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.525</v>
+        <v>0.192857142857143</v>
       </c>
       <c r="E9" t="n">
-        <v>2.22407410134712</v>
+        <v>0.708660102968926</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0444839058001064</v>
+        <v>0.491048701605223</v>
       </c>
       <c r="G9" t="n">
-        <v>0.289145387700692</v>
+        <v>0.756051387063227</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.425</v>
+        <v>-0.167857142857143</v>
       </c>
       <c r="E10" t="n">
-        <v>1.69285301631857</v>
+        <v>-0.6139283620727</v>
       </c>
       <c r="F10" t="n">
-        <v>0.114295475480522</v>
+        <v>0.549855554227802</v>
       </c>
       <c r="G10" t="n">
-        <v>0.371460295311697</v>
+        <v>0.756051387063227</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00357142857142857</v>
+        <v>0.260714285714286</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0128770509652542</v>
+        <v>0.973692917115073</v>
       </c>
       <c r="F11" t="n">
-        <v>0.989921406880978</v>
+        <v>0.347979459862794</v>
       </c>
       <c r="G11" t="n">
-        <v>0.989921406880978</v>
+        <v>0.756051387063227</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.35</v>
+        <v>-0.535714285714286</v>
       </c>
       <c r="E12" t="n">
-        <v>1.34715062810913</v>
+        <v>-2.28747855498907</v>
       </c>
       <c r="F12" t="n">
-        <v>0.200945350816293</v>
+        <v>0.0395669722295495</v>
       </c>
       <c r="G12" t="n">
-        <v>0.522457912122363</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.260714285714286</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.973692917115073</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.347979459862794</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.646247568316617</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.157142857142857</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.573714526046661</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.575952600603795</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.870349885864411</v>
+        <v>0.217618347262522</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.178571428571429</v>
+        <v>0.0678571428571429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.654366100445603</v>
+        <v>0.245227646009749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.524284360046553</v>
+        <v>0.810108818710513</v>
       </c>
       <c r="G2" t="n">
-        <v>0.742154576211639</v>
+        <v>0.901942761851601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.164285714285714</v>
+        <v>-0.235714285714286</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6004996783241</v>
+        <v>-0.874521871729162</v>
       </c>
       <c r="F3" t="n">
-        <v>0.558497373248601</v>
+        <v>0.397702945903273</v>
       </c>
       <c r="G3" t="n">
-        <v>0.742154576211639</v>
+        <v>0.878273300965591</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.357142857142857</v>
+        <v>-0.0642857142857143</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.37861698644752</v>
+        <v>-0.232265873153491</v>
       </c>
       <c r="F4" t="n">
-        <v>0.191274763431579</v>
+        <v>0.819947965319638</v>
       </c>
       <c r="G4" t="n">
-        <v>0.742154576211639</v>
+        <v>0.901942761851601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.242857142857143</v>
+        <v>0.153571428571429</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.90265758615802</v>
+        <v>0.560356865859059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.383128341839342</v>
+        <v>0.584764094941016</v>
       </c>
       <c r="G5" t="n">
-        <v>0.742154576211639</v>
+        <v>0.878273300965591</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.160714285714286</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.587095265748098</v>
+        <v>0.654366100445603</v>
       </c>
       <c r="F6" t="n">
-        <v>0.567196704580345</v>
+        <v>0.524284360046553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.742154576211639</v>
+        <v>0.878273300965591</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.239285714285714</v>
+        <v>0.132142857142857</v>
       </c>
       <c r="E7" t="n">
-        <v>0.888570600065875</v>
+        <v>0.480662933137168</v>
       </c>
       <c r="F7" t="n">
-        <v>0.390379311920236</v>
+        <v>0.638744218884067</v>
       </c>
       <c r="G7" t="n">
-        <v>0.742154576211639</v>
+        <v>0.878273300965591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.489285714285714</v>
+        <v>0.517857142857143</v>
       </c>
       <c r="E8" t="n">
-        <v>2.02281514740178</v>
+        <v>2.18262099840031</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0641603863145405</v>
+        <v>0.0480040773665583</v>
       </c>
       <c r="G8" t="n">
-        <v>0.494457789477153</v>
+        <v>0.528044851032142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.471428571428571</v>
+        <v>0.428571428571428</v>
       </c>
       <c r="E9" t="n">
-        <v>1.92737464584669</v>
+        <v>1.71026313764871</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0760704291503312</v>
+        <v>0.110960214260877</v>
       </c>
       <c r="G9" t="n">
-        <v>0.494457789477153</v>
+        <v>0.610281178434822</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.121428571428571</v>
+        <v>-0.232142857142857</v>
       </c>
       <c r="E10" t="n">
-        <v>0.441080862981928</v>
+        <v>-0.860510661125327</v>
       </c>
       <c r="F10" t="n">
-        <v>0.66640111372339</v>
+        <v>0.405098740693649</v>
       </c>
       <c r="G10" t="n">
-        <v>0.742154576211639</v>
+        <v>0.878273300965591</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.114285714285714</v>
+        <v>-0.00357142857142857</v>
       </c>
       <c r="E11" t="n">
-        <v>0.41478067789217</v>
+        <v>-0.0128770509652542</v>
       </c>
       <c r="F11" t="n">
-        <v>0.685065762656897</v>
+        <v>0.989921406880978</v>
       </c>
       <c r="G11" t="n">
-        <v>0.742154576211639</v>
+        <v>0.989921406880978</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.132142857142857</v>
+        <v>-0.346428571428571</v>
       </c>
       <c r="E12" t="n">
-        <v>0.480662933137168</v>
+        <v>-1.33151845580652</v>
       </c>
       <c r="F12" t="n">
-        <v>0.638744218884067</v>
+        <v>0.205895992093551</v>
       </c>
       <c r="G12" t="n">
-        <v>0.742154576211639</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00357142857142857</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.0128770509652542</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.989921406880978</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.989921406880978</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.178571428571429</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.654366100445603</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.524284360046553</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.742154576211639</v>
+        <v>0.754951971009688</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00714285714285714</v>
+        <v>-0.0357142857142857</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0257545946952327</v>
+        <v>-0.128851890580845</v>
       </c>
       <c r="F2" t="n">
+        <v>0.899446993472087</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.979844227761598</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.989921406880978</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.192857142857143</v>
+        <v>-0.157142857142857</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.708660102968926</v>
+        <v>-0.573714526046661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.491048701605223</v>
+        <v>0.575952600603795</v>
       </c>
       <c r="G3" t="n">
-        <v>0.911947588695414</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.332142857142857</v>
+        <v>-0.114285714285714</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.26963651854388</v>
+        <v>-0.41478067789217</v>
       </c>
       <c r="F4" t="n">
-        <v>0.226471759070724</v>
+        <v>0.685065762656897</v>
       </c>
       <c r="G4" t="n">
-        <v>0.911947588695414</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.142857142857143</v>
+        <v>0.282142857142857</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.520416499866533</v>
+        <v>1.06036043455401</v>
       </c>
       <c r="F5" t="n">
-        <v>0.611522228764465</v>
+        <v>0.308284456820055</v>
       </c>
       <c r="G5" t="n">
-        <v>0.957401331203334</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00357142857142857</v>
+        <v>0.00714285714285714</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0128770509652542</v>
+        <v>0.0257545946952327</v>
       </c>
       <c r="F6" t="n">
-        <v>0.989921406880978</v>
+        <v>0.979844227761598</v>
       </c>
       <c r="G6" t="n">
-        <v>0.989921406880978</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0785714285714286</v>
+        <v>-0.0357142857142857</v>
       </c>
       <c r="E7" t="n">
-        <v>0.284171835544338</v>
+        <v>-0.128851890580845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.780754552309047</v>
+        <v>0.899446993472087</v>
       </c>
       <c r="G7" t="n">
-        <v>0.957401331203334</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.314285714285714</v>
+        <v>0.482142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>1.19365775688834</v>
+        <v>1.98425459722429</v>
       </c>
       <c r="F8" t="n">
-        <v>0.253940016323672</v>
+        <v>0.0687495377206437</v>
       </c>
       <c r="G8" t="n">
-        <v>0.911947588695414</v>
+        <v>0.75624491492708</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.421428571428571</v>
+        <v>0.246428571428571</v>
       </c>
       <c r="E9" t="n">
-        <v>1.67553938265939</v>
+        <v>0.916783578893438</v>
       </c>
       <c r="F9" t="n">
-        <v>0.117699395855416</v>
+        <v>0.375950515973805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.911947588695414</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.25</v>
+        <v>-0.210714285714286</v>
       </c>
       <c r="E10" t="n">
-        <v>0.930949336251263</v>
+        <v>-0.777190891009981</v>
       </c>
       <c r="F10" t="n">
-        <v>0.368846291783931</v>
+        <v>0.450957865215285</v>
       </c>
       <c r="G10" t="n">
-        <v>0.911947588695414</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0678571428571429</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E11" t="n">
-        <v>0.245227646009749</v>
+        <v>0.258198889747161</v>
       </c>
       <c r="F11" t="n">
-        <v>0.810108818710513</v>
+        <v>0.800295987397054</v>
       </c>
       <c r="G11" t="n">
-        <v>0.957401331203334</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.257142857142857</v>
+        <v>-0.335714285714286</v>
       </c>
       <c r="E12" t="n">
-        <v>0.959403223600247</v>
+        <v>-1.28501221666837</v>
       </c>
       <c r="F12" t="n">
-        <v>0.354860363650609</v>
+        <v>0.221211537639326</v>
       </c>
       <c r="G12" t="n">
-        <v>0.911947588695414</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.258198889747161</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.800295987397054</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.957401331203334</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.217857142857143</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.804826493639811</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.435392673515538</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.911947588695414</v>
+        <v>0.979844227761598</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.425</v>
+        <v>-0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.69285301631857</v>
+        <v>-2.70416345659799</v>
       </c>
       <c r="F2" t="n">
-        <v>0.114295475480522</v>
+        <v>0.0180500879415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.273866645578177</v>
+        <v>0.049637741839125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.682142857142857</v>
+        <v>0.382142857142857</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.36356315508022</v>
+        <v>1.49099751546869</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00508632646897726</v>
+        <v>0.159823629986967</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0330611220483522</v>
+        <v>0.21975749123208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4</v>
+        <v>-0.607142857142857</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.57359158493889</v>
+        <v>-2.75497713055825</v>
       </c>
       <c r="F4" t="n">
-        <v>0.139595129372145</v>
+        <v>0.0163813067683071</v>
       </c>
       <c r="G4" t="n">
-        <v>0.273866645578177</v>
+        <v>0.049637741839125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.392857142857143</v>
+        <v>0.735714285714286</v>
       </c>
       <c r="E5" t="n">
-        <v>1.54030809243081</v>
+        <v>3.91656106318704</v>
       </c>
       <c r="F5" t="n">
-        <v>0.147466655311326</v>
+        <v>0.00176986864214427</v>
       </c>
       <c r="G5" t="n">
-        <v>0.273866645578177</v>
+        <v>0.019468555063587</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.628571428571428</v>
+        <v>-0.639285714285714</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.9139711855431</v>
+        <v>-2.99748954833848</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0120795391759058</v>
+        <v>0.0102884466195942</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0392585023216937</v>
+        <v>0.049637741839125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.328571428571429</v>
+        <v>-0.403571428571428</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.25432220027765</v>
+        <v>-1.59036060370339</v>
       </c>
       <c r="F7" t="n">
-        <v>0.23180969720616</v>
+        <v>0.135767996503656</v>
       </c>
       <c r="G7" t="n">
-        <v>0.342102879432838</v>
+        <v>0.21975749123208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00357142857142857</v>
+        <v>0.232142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0128770509652542</v>
+        <v>0.860510661125327</v>
       </c>
       <c r="F8" t="n">
-        <v>0.989921406880978</v>
+        <v>0.405098740693649</v>
       </c>
       <c r="G8" t="n">
-        <v>0.989921406880978</v>
+        <v>0.443140934823514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.296428571428571</v>
+        <v>-0.214285714285714</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1190856914849</v>
+        <v>-0.790992066456966</v>
       </c>
       <c r="F9" t="n">
-        <v>0.283355428434263</v>
+        <v>0.443140934823514</v>
       </c>
       <c r="G9" t="n">
-        <v>0.342102879432838</v>
+        <v>0.443140934823514</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.753571428571428</v>
+        <v>0.385714285714286</v>
       </c>
       <c r="E10" t="n">
-        <v>4.13322302468662</v>
+        <v>1.50735430417727</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00117758302348883</v>
+        <v>0.15563079458596</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0153085793053548</v>
+        <v>0.21975749123208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.214285714285714</v>
+        <v>0.317857142857143</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.790992066456966</v>
+        <v>1.20873699952121</v>
       </c>
       <c r="F11" t="n">
-        <v>0.443140934823514</v>
+        <v>0.248290565817018</v>
       </c>
       <c r="G11" t="n">
-        <v>0.480069346058807</v>
+        <v>0.303466247109689</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.628571428571428</v>
+        <v>-0.439285714285714</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9139711855431</v>
+        <v>-1.76308982191951</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0120795391759058</v>
+        <v>0.101360571193472</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0392585023216937</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.317857142857143</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.20873699952121</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.248290565817018</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.342102879432838</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.292857142857143</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.10432943513766</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.289471667212401</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.342102879432838</v>
+        <v>0.21975749123208</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0717496003334175</v>
+        <v>-0.00717496003334175</v>
       </c>
       <c r="E2" t="n">
-        <v>0.259365331456823</v>
+        <v>-0.0258703522117207</v>
       </c>
       <c r="F2" t="n">
-        <v>0.799415264937861</v>
+        <v>0.979753656625192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0412560201917151</v>
+        <v>0.143499200666835</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.148877449297363</v>
+        <v>0.522804526501402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.883935009439022</v>
+        <v>0.609905390370286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0914807404251073</v>
+        <v>0.0107624400500126</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.331227387834397</v>
+        <v>0.0388067770112516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.74575126155103</v>
+        <v>0.969634067313828</v>
       </c>
       <c r="G4" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.118386840550139</v>
+        <v>-0.10224318047512</v>
       </c>
       <c r="E5" t="n">
-        <v>0.429872883365625</v>
+        <v>-0.370585105377105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.674327856137202</v>
+        <v>0.7169148536404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0609871602834049</v>
+        <v>0.10224318047512</v>
       </c>
       <c r="E6" t="n">
-        <v>0.220302415336035</v>
+        <v>0.370585105377105</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8290575765356</v>
+        <v>0.7169148536404</v>
       </c>
       <c r="G6" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.105830660491791</v>
+        <v>0.0789245603667593</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.383732852590239</v>
+        <v>0.285457006298828</v>
       </c>
       <c r="F7" t="n">
-        <v>0.707378976102928</v>
+        <v>0.779791507797579</v>
       </c>
       <c r="G7" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.197311400916898</v>
+        <v>0.044843500208386</v>
       </c>
       <c r="E8" t="n">
-        <v>0.725682666948952</v>
+        <v>0.161848354892665</v>
       </c>
       <c r="F8" t="n">
-        <v>0.480894166974442</v>
+        <v>0.873913706886497</v>
       </c>
       <c r="G8" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0807183003750947</v>
+        <v>0.218836281016923</v>
       </c>
       <c r="E9" t="n">
-        <v>0.291986736949278</v>
+        <v>0.808625221124944</v>
       </c>
       <c r="F9" t="n">
-        <v>0.774904316932002</v>
+        <v>0.433280499152867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.123768060575145</v>
+        <v>0.256504821191968</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.449709829036912</v>
+        <v>0.956854823646126</v>
       </c>
       <c r="F10" t="n">
-        <v>0.660326567300537</v>
+        <v>0.356097527461551</v>
       </c>
       <c r="G10" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0843057803917656</v>
+        <v>-0.0914807404251073</v>
       </c>
       <c r="E11" t="n">
-        <v>0.305054830372386</v>
+        <v>-0.331227387834397</v>
       </c>
       <c r="F11" t="n">
-        <v>0.765153583796111</v>
+        <v>0.74575126155103</v>
       </c>
       <c r="G11" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.129149280600152</v>
+        <v>-0.0484309802250568</v>
       </c>
       <c r="E12" t="n">
-        <v>0.469587068686676</v>
+        <v>-0.174825534769435</v>
       </c>
       <c r="F12" t="n">
-        <v>0.646429063350437</v>
+        <v>0.863910158191933</v>
       </c>
       <c r="G12" t="n">
-        <v>0.883935009439022</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0914807404251073</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.331227387834397</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.74575126155103</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.883935009439022</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.310317021442031</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.17696711609459</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.26030929240151</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.883935009439022</v>
+        <v>0.979753656625192</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0925112376316003</v>
+        <v>0.0991191831767146</v>
       </c>
       <c r="E2" t="n">
-        <v>0.321848529917491</v>
+        <v>0.345058137608938</v>
       </c>
       <c r="F2" t="n">
-        <v>0.753104842158374</v>
+        <v>0.736023383755644</v>
       </c>
       <c r="G2" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0110132425751905</v>
+        <v>-0.132158910902286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0381533052988319</v>
+        <v>-0.46186310962737</v>
       </c>
       <c r="F3" t="n">
-        <v>0.970192834119859</v>
+        <v>0.652440458041441</v>
       </c>
       <c r="G3" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.151982747537629</v>
+        <v>-0.248899282199305</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.532671649691602</v>
+        <v>-0.890228452610361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.603984996702905</v>
+        <v>0.390842015254325</v>
       </c>
       <c r="G4" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.110132425751905</v>
+        <v>0.165198638627858</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.383844872037334</v>
+        <v>0.580237146253636</v>
       </c>
       <c r="F5" t="n">
-        <v>0.707807929973688</v>
+        <v>0.572489335778481</v>
       </c>
       <c r="G5" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0374450247556477</v>
+        <v>-0.118943019812057</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.129804403972826</v>
+        <v>-0.414976591963709</v>
       </c>
       <c r="F6" t="n">
-        <v>0.898871627481408</v>
+        <v>0.685481981280161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.114537722781981</v>
+        <v>0.114537722781981</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.399398794051085</v>
+        <v>0.399398794051085</v>
       </c>
       <c r="F7" t="n">
         <v>0.696616418849427</v>
       </c>
       <c r="G7" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0925112376316003</v>
+        <v>0.202643663383505</v>
       </c>
       <c r="E8" t="n">
-        <v>0.321848529917491</v>
+        <v>0.716851077535768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.753104842158374</v>
+        <v>0.487184653179536</v>
       </c>
       <c r="G8" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.229075445563963</v>
+        <v>0.160793341597781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.815218360831655</v>
+        <v>0.564347712691896</v>
       </c>
       <c r="F9" t="n">
-        <v>0.430830581603804</v>
+        <v>0.582912376280973</v>
       </c>
       <c r="G9" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.156388044567705</v>
+        <v>0.063876806936105</v>
       </c>
       <c r="E10" t="n">
-        <v>0.548492903529079</v>
+        <v>0.221728566048358</v>
       </c>
       <c r="F10" t="n">
-        <v>0.593411482796674</v>
+        <v>0.828253649971719</v>
       </c>
       <c r="G10" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.12775361387221</v>
+        <v>0.0484582673308382</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.446207755179622</v>
+        <v>0.168061799769335</v>
       </c>
       <c r="F11" t="n">
-        <v>0.663392093484309</v>
+        <v>0.869333899732566</v>
       </c>
       <c r="G11" t="n">
-        <v>0.970192834119859</v>
+        <v>0.869333899732566</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0506609158458763</v>
+        <v>-0.176211881203048</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.175720200719443</v>
+        <v>-0.620119327930314</v>
       </c>
       <c r="F12" t="n">
-        <v>0.863444140009189</v>
+        <v>0.546775095487439</v>
       </c>
       <c r="G12" t="n">
-        <v>0.970192834119859</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0484582673308382</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.168061799769335</v>
-      </c>
-      <c r="F13" t="n">
         <v>0.869333899732566</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.970192834119859</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.145374801992515</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.509000372563053</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.619981070322052</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.970192834119859</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -2501,24 +2219,24 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.260714285714286</v>
+        <v>0.217857142857143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.110132425751905</v>
+        <v>0.132158910902286</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2558,22 +2276,22 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2584,19 +2302,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,24 +2323,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.192857142857143</v>
+        <v>0.157142857142857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -2631,7 +2349,7 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.392857142857143</v>
+        <v>0.403571428571428</v>
       </c>
     </row>
   </sheetData>
